--- a/sources/king_step8c.xlsx
+++ b/sources/king_step8c.xlsx
@@ -1423,11 +1423,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>67ff2023-6e37-4766-ab77-10e230c708b4</t>
@@ -1490,11 +1485,6 @@
           <t>3+4</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>c4c3cd71-ed27-44df-a655-fb09f78b6be8</t>
@@ -1557,11 +1547,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>f8794d93-a444-4657-859f-d2548700e248</t>
@@ -1622,11 +1607,6 @@
       <c r="V17" t="inlineStr">
         <is>
           <t>1+2</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">

--- a/sources/king_step8c.xlsx
+++ b/sources/king_step8c.xlsx
@@ -10444,12 +10444,12 @@
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="T128" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="X128" t="inlineStr">

--- a/sources/king_step8c.xlsx
+++ b/sources/king_step8c.xlsx
@@ -1423,6 +1423,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>67ff2023-6e37-4766-ab77-10e230c708b4</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>67ff2023-6e37-4766-ab77-10e230c708b4</t>
@@ -1485,6 +1490,11 @@
           <t>3+4</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>c4c3cd71-ed27-44df-a655-fb09f78b6be8</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>c4c3cd71-ed27-44df-a655-fb09f78b6be8</t>
@@ -1547,6 +1557,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>f8794d93-a444-4657-859f-d2548700e248</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>f8794d93-a444-4657-859f-d2548700e248</t>
@@ -1609,6 +1624,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>9821af5c-9a74-43da-8d33-7092f2b7ff7b</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>9821af5c-9a74-43da-8d33-7092f2b7ff7b</t>
@@ -1676,6 +1696,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>7df0cfa5-026b-4ff9-9f39-55c477962d0f</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>7df0cfa5-026b-4ff9-9f39-55c477962d0f</t>
@@ -1728,6 +1753,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>f8490fa0-7b1f-4f39-99ab-da6ae361ed20</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>f8490fa0-7b1f-4f39-99ab-da6ae361ed20</t>
@@ -1785,6 +1815,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>68f074ca-3602-4223-bca2-a6b2ec87ef2a</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>68f074ca-3602-4223-bca2-a6b2ec87ef2a</t>
@@ -1842,6 +1877,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>0176585b-588a-49e1-9572-4bdd7101f82a</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>0176585b-588a-49e1-9572-4bdd7101f82a</t>
@@ -1899,6 +1939,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>00ddf7e7-6010-4a77-9ae6-40ef2f2a707a</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>00ddf7e7-6010-4a77-9ae6-40ef2f2a707a</t>
@@ -1956,6 +2001,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>b6c23f31-cb1a-450f-9a17-e7cc5b124033</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>b6c23f31-cb1a-450f-9a17-e7cc5b124033</t>
@@ -2013,6 +2063,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12308a0d-a04e-49ad-a92e-7b32fb03c49f</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>12308a0d-a04e-49ad-a92e-7b32fb03c49f</t>
@@ -2070,6 +2125,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>6c0cc2bf-f0ad-4b46-a1ff-2a7de8bdb37f</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>6c0cc2bf-f0ad-4b46-a1ff-2a7de8bdb37f</t>
@@ -2127,6 +2187,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>377bd68e-1783-43e2-8c72-05143260300a</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>377bd68e-1783-43e2-8c72-05143260300a</t>
@@ -2184,6 +2249,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>f57394c8-7aba-414b-af3e-d37941cae2e3</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>f57394c8-7aba-414b-af3e-d37941cae2e3</t>
@@ -2251,6 +2321,11 @@
           <t>The Counter Hit Stomach Smash is NOT a throw but is required before you can do the 2 throw follow ups.</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>b2d4546c-7d86-4fee-a8f7-dbe4e5857d92</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>b2d4546c-7d86-4fee-a8f7-dbe4e5857d92</t>
@@ -2303,6 +2378,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>829ce921-0e10-4ab2-bbbc-911f844eceef</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>829ce921-0e10-4ab2-bbbc-911f844eceef</t>
@@ -2360,6 +2440,11 @@
           <t>3+4</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>db0aa370-9079-45e2-b39c-7472d8bae8a4</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>db0aa370-9079-45e2-b39c-7472d8bae8a4</t>
@@ -2427,6 +2512,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>6294b53d-e480-4df4-be9f-98a25b5e6a95</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>6294b53d-e480-4df4-be9f-98a25b5e6a95</t>
@@ -2489,6 +2579,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16314dd7-17de-43e3-89e8-146678a228d1</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>16314dd7-17de-43e3-89e8-146678a228d1</t>
@@ -2551,6 +2646,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>ab65c71e-57c4-4826-b7e0-038c4501bdc6</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>ab65c71e-57c4-4826-b7e0-038c4501bdc6</t>
@@ -2608,6 +2708,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>fe0b77cb-f2dd-4ba4-b684-d4ecf9d4a053</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>fe0b77cb-f2dd-4ba4-b684-d4ecf9d4a053</t>
@@ -2663,6 +2768,11 @@
       <c r="V35" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>a7a77dd9-2c48-4420-8555-24aab9d0520c</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -2882,6 +2992,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>014ddb56-1613-49f0-9e34-a5e1f6c785fe</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>014ddb56-1613-49f0-9e34-a5e1f6c785fe</t>
@@ -2944,6 +3059,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>8b30b6c0-0bc1-4441-8820-964886587202</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>8b30b6c0-0bc1-4441-8820-964886587202</t>
@@ -3001,6 +3121,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>1a628a44-4c66-4d94-b410-673005311f11</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>1a628a44-4c66-4d94-b410-673005311f11</t>
@@ -3058,6 +3183,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>912252eb-66d4-4874-abc8-0c9951b57b07</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>912252eb-66d4-4874-abc8-0c9951b57b07</t>
@@ -3115,6 +3245,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>78755529-5600-440c-8380-ad656059ff13</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>78755529-5600-440c-8380-ad656059ff13</t>
@@ -3177,6 +3312,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>3d784cd2-6e86-46a8-bbd0-6f0b4d5c473c</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>3d784cd2-6e86-46a8-bbd0-6f0b4d5c473c</t>
@@ -3239,6 +3379,11 @@
           <t>3+4</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>97fdc64c-6825-4fbc-b64c-406c522a9288</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>97fdc64c-6825-4fbc-b64c-406c522a9288</t>
@@ -3301,6 +3446,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>4b9555c8-11ce-4fb0-af28-67c8956588ae</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>4b9555c8-11ce-4fb0-af28-67c8956588ae</t>
@@ -3363,6 +3513,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>cb6d3d00-45b4-40eb-8e80-dff09bade591</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>cb6d3d00-45b4-40eb-8e80-dff09bade591</t>
@@ -3423,6 +3578,11 @@
       <c r="V48" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>44cede5f-e666-42c2-b9ea-20ca0d73478e</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -10669,6 +10829,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>d14fb2bb-b9cb-4ac9-9db3-e052c90daa2f</t>
+        </is>
+      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>d14fb2bb-b9cb-4ac9-9db3-e052c90daa2f</t>
@@ -10721,6 +10886,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>754287bc-eb16-4fb1-adf5-9ba198ef61bc</t>
+        </is>
+      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>754287bc-eb16-4fb1-adf5-9ba198ef61bc</t>
@@ -10778,6 +10948,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>610d1988-6af6-4bcc-a947-eb4020bc3119</t>
+        </is>
+      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>610d1988-6af6-4bcc-a947-eb4020bc3119</t>
@@ -10835,6 +11010,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>ffa2eb74-b7c8-48f6-b268-2882ba61fae0</t>
+        </is>
+      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>ffa2eb74-b7c8-48f6-b268-2882ba61fae0</t>
@@ -10892,6 +11072,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>318177e8-8c06-4cfe-a628-4c3f588e36e9</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>318177e8-8c06-4cfe-a628-4c3f588e36e9</t>
@@ -10959,6 +11144,11 @@
           <t>After the initial grab use 3+4 to escape.</t>
         </is>
       </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>e9174a35-b2b1-40d7-8704-552434c99980</t>
+        </is>
+      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>e9174a35-b2b1-40d7-8704-552434c99980</t>
@@ -11016,6 +11206,11 @@
           <t>Double Arm Face Buster is not additional damage to the Jaguar Driver, it add 5 points of damage.</t>
         </is>
       </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>61fbd176-0a6e-4368-89b2-fae51c957338</t>
+        </is>
+      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>61fbd176-0a6e-4368-89b2-fae51c957338</t>
@@ -11073,6 +11268,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>e370e475-82e9-42c2-9dda-e815185d01ba</t>
+        </is>
+      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>e370e475-82e9-42c2-9dda-e815185d01ba</t>
@@ -11135,6 +11335,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>d0dc416c-d281-41de-a830-391175b9c733</t>
+        </is>
+      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>d0dc416c-d281-41de-a830-391175b9c733</t>
@@ -11187,6 +11392,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>c1efc095-a281-425f-89ef-e6a21a09748e</t>
+        </is>
+      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>c1efc095-a281-425f-89ef-e6a21a09748e</t>
@@ -11244,6 +11454,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>ca3bdbfd-726c-4c6a-8a68-16d368d953de</t>
+        </is>
+      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>ca3bdbfd-726c-4c6a-8a68-16d368d953de</t>
@@ -11301,6 +11516,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>576fbd03-9817-4433-aee9-a05fb2873ee9</t>
+        </is>
+      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>576fbd03-9817-4433-aee9-a05fb2873ee9</t>
@@ -11358,6 +11578,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>bf90b650-01f4-4fc9-88b8-319864f95c86</t>
+        </is>
+      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>bf90b650-01f4-4fc9-88b8-319864f95c86</t>
@@ -11415,6 +11640,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>9cb56a53-599f-4719-9b84-f7e40bb6afa8</t>
+        </is>
+      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>9cb56a53-599f-4719-9b84-f7e40bb6afa8</t>
@@ -11472,6 +11702,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>c053f961-d2f8-4fbd-83ae-34fca200b9b7</t>
+        </is>
+      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>c053f961-d2f8-4fbd-83ae-34fca200b9b7</t>
@@ -11544,6 +11779,11 @@
           <t>Escape with 1 if the multi was started with 1+3 and 2 if the multi was started with 2+4.</t>
         </is>
       </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>8a657c3c-5962-4744-8afb-8db34e185b60</t>
+        </is>
+      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>8a657c3c-5962-4744-8afb-8db34e185b60</t>
@@ -11601,6 +11841,11 @@
           <t>Escape with 1 if the multi was started with 1+3 and 2 if the multi was started with 2+4.</t>
         </is>
       </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>e9b59331-5359-43c8-a2fe-c2f1c768010e</t>
+        </is>
+      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>e9b59331-5359-43c8-a2fe-c2f1c768010e</t>
@@ -11658,6 +11903,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>a35b6adb-c2ae-4dcc-8c1c-e89ddf41df28</t>
+        </is>
+      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>a35b6adb-c2ae-4dcc-8c1c-e89ddf41df28</t>
@@ -11715,6 +11965,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>a076bd88-cfd9-4b82-b29b-751f8994df70</t>
+        </is>
+      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>a076bd88-cfd9-4b82-b29b-751f8994df70</t>
@@ -11772,6 +12027,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>897562ea-11c8-48e1-bdd7-3508028d9455</t>
+        </is>
+      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>897562ea-11c8-48e1-bdd7-3508028d9455</t>
@@ -11829,6 +12089,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>0499e709-28d1-44ad-884c-143bf75b7436</t>
+        </is>
+      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>0499e709-28d1-44ad-884c-143bf75b7436</t>
@@ -11886,6 +12151,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>988107cd-c43e-41b1-bec3-f6450eebd275</t>
+        </is>
+      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>988107cd-c43e-41b1-bec3-f6450eebd275</t>
@@ -11943,6 +12213,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>54aa2be5-501e-441f-b759-e6eaa8b2c7aa</t>
+        </is>
+      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>54aa2be5-501e-441f-b759-e6eaa8b2c7aa</t>
@@ -12000,6 +12275,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>e36e2276-3cc6-43b4-bef5-0d88f962c067</t>
+        </is>
+      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>e36e2276-3cc6-43b4-bef5-0d88f962c067</t>
@@ -12057,6 +12337,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>91806b57-15f2-453a-9e66-6e9265eb3f74</t>
+        </is>
+      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>91806b57-15f2-453a-9e66-6e9265eb3f74</t>
@@ -12114,6 +12399,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>0d22dd12-3fab-495f-bd30-0dd66be69ec9</t>
+        </is>
+      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>0d22dd12-3fab-495f-bd30-0dd66be69ec9</t>
@@ -12171,6 +12461,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>0b34d2a0-d07c-4603-9984-9e48ffa8b289</t>
+        </is>
+      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>0b34d2a0-d07c-4603-9984-9e48ffa8b289</t>
@@ -12228,6 +12523,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>3a88bc91-07bf-4196-bbfc-65d00fdc5cdb</t>
+        </is>
+      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>3a88bc91-07bf-4196-bbfc-65d00fdc5cdb</t>
@@ -12285,6 +12585,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>88d1f06b-09b4-4f3b-b26f-6b7eb09839b9</t>
+        </is>
+      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>88d1f06b-09b4-4f3b-b26f-6b7eb09839b9</t>
@@ -12347,6 +12652,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>21a93725-b013-4fd7-b6a0-53b29c951345</t>
+        </is>
+      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>21a93725-b013-4fd7-b6a0-53b29c951345</t>
@@ -12409,6 +12719,11 @@
           <t>If grabbed from the side or back then Cannonball will be the 1st part of the Multi Throw.</t>
         </is>
       </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>e5cfb3e7-d8eb-43a9-95a5-78b47376b89c</t>
+        </is>
+      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>e5cfb3e7-d8eb-43a9-95a5-78b47376b89c</t>
@@ -12466,6 +12781,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>d29031f4-9c39-4518-8ca7-d1d579f731d3</t>
+        </is>
+      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>d29031f4-9c39-4518-8ca7-d1d579f731d3</t>
@@ -12518,6 +12838,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>cf747642-f5e0-4884-9c87-bf258ea86c4c</t>
+        </is>
+      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>cf747642-f5e0-4884-9c87-bf258ea86c4c</t>
@@ -12575,6 +12900,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>90ec3fb9-f4d7-421a-99e2-e37e4a49ce00</t>
+        </is>
+      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>90ec3fb9-f4d7-421a-99e2-e37e4a49ce00</t>
@@ -12632,6 +12962,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>334b113e-5fa6-4350-8c7f-d1443e15e6b7</t>
+        </is>
+      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>334b113e-5fa6-4350-8c7f-d1443e15e6b7</t>
@@ -12689,6 +13024,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>58f13036-58ee-4611-a14d-d783777422a0</t>
+        </is>
+      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>58f13036-58ee-4611-a14d-d783777422a0</t>
@@ -12746,6 +13086,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>f7973f34-41fe-4bf5-95c3-8fb79ee2452d</t>
+        </is>
+      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>f7973f34-41fe-4bf5-95c3-8fb79ee2452d</t>
@@ -12803,6 +13148,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>0515905e-bcfb-496f-bbfc-01dedb07caa4</t>
+        </is>
+      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>0515905e-bcfb-496f-bbfc-01dedb07caa4</t>
@@ -12860,6 +13210,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>fefe8385-3ffe-4743-8071-1a48c86080c5</t>
+        </is>
+      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>fefe8385-3ffe-4743-8071-1a48c86080c5</t>
@@ -12915,6 +13270,11 @@
       <c r="V171" t="inlineStr">
         <is>
           <t>2</t>
+        </is>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>cd229188-1f00-4e2c-beb7-0ecdab35b8dc</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -13124,6 +13484,11 @@
           <t>hhmmhLLLmM</t>
         </is>
       </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>540396d1-00a1-4033-9fce-7dbbcf91bebf</t>
+        </is>
+      </c>
       <c r="AA175" t="inlineStr">
         <is>
           <t>540396d1-00a1-4033-9fce-7dbbcf91bebf</t>
@@ -13171,6 +13536,11 @@
           <t>hhmmhLLLmh</t>
         </is>
       </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>53b541e0-d1fa-4602-8e8e-198dc6d57441</t>
+        </is>
+      </c>
       <c r="AA176" t="inlineStr">
         <is>
           <t>53b541e0-d1fa-4602-8e8e-198dc6d57441</t>
@@ -13218,6 +13588,11 @@
           <t>hhmmhmLLmM</t>
         </is>
       </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>d76e55af-5e37-469f-b459-858d5c452608</t>
+        </is>
+      </c>
       <c r="AA177" t="inlineStr">
         <is>
           <t>d76e55af-5e37-469f-b459-858d5c452608</t>
@@ -13265,6 +13640,11 @@
           <t>hhmmhmLLmh</t>
         </is>
       </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>10ceada9-d82e-41bd-b56c-5a3fa1400921</t>
+        </is>
+      </c>
       <c r="AA178" t="inlineStr">
         <is>
           <t>10ceada9-d82e-41bd-b56c-5a3fa1400921</t>
@@ -13312,6 +13692,11 @@
           <t>hhmmhmLLlthrow</t>
         </is>
       </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>5c5c8a42-acd0-4b4b-88f6-39a67110202e</t>
+        </is>
+      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>5c5c8a42-acd0-4b4b-88f6-39a67110202e</t>
@@ -13359,6 +13744,11 @@
           <t>hmmhLLLmM</t>
         </is>
       </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>47c1d8e6-c95b-4542-b264-13a374b2c050</t>
+        </is>
+      </c>
       <c r="AA180" t="inlineStr">
         <is>
           <t>47c1d8e6-c95b-4542-b264-13a374b2c050</t>
@@ -13406,6 +13796,11 @@
           <t>hmmhLLLmh</t>
         </is>
       </c>
+      <c r="Z181" t="inlineStr">
+        <is>
+          <t>76d4a800-1555-4b0e-a6b7-bdcb47516018</t>
+        </is>
+      </c>
       <c r="AA181" t="inlineStr">
         <is>
           <t>76d4a800-1555-4b0e-a6b7-bdcb47516018</t>
@@ -13453,6 +13848,11 @@
           <t>hmmhmLLmM</t>
         </is>
       </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>d3e32834-6f80-4957-ac5b-a1be0e260a44</t>
+        </is>
+      </c>
       <c r="AA182" t="inlineStr">
         <is>
           <t>d3e32834-6f80-4957-ac5b-a1be0e260a44</t>
@@ -13500,6 +13900,11 @@
           <t>hmmhmLLmh</t>
         </is>
       </c>
+      <c r="Z183" t="inlineStr">
+        <is>
+          <t>3de5ed24-6134-418b-ba3e-f25a1039677a</t>
+        </is>
+      </c>
       <c r="AA183" t="inlineStr">
         <is>
           <t>3de5ed24-6134-418b-ba3e-f25a1039677a</t>
@@ -13545,6 +13950,11 @@
       <c r="T184" t="inlineStr">
         <is>
           <t>hmmhmLLlthrow</t>
+        </is>
+      </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>9aa5afc6-6646-4750-b84c-b3114de16321</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
